--- a/AI Planning/Job Scheduling/Flow Shop/problemset/solution/def/reposteria-200j-4m-30_180tr-constantd_def.xlsx
+++ b/AI Planning/Job Scheduling/Flow Shop/problemset/solution/def/reposteria-200j-4m-30_180tr-constantd_def.xlsx
@@ -458,7 +458,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brownies #Ok55</t>
+          <t>Panetone #Uq52</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -479,7 +479,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Brownies #Ok55</t>
+          <t>Panetone #Uq52</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -500,7 +500,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Brownies #Ok55</t>
+          <t>Panetone #Uq52</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Brownies #Ok55</t>
+          <t>Panetone #Uq52</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -542,7 +542,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Éclairs #Ba54</t>
+          <t>Macarons #BX96</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Éclairs #Ba54</t>
+          <t>Macarons #BX96</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Éclairs #Ba54</t>
+          <t>Macarons #BX96</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Éclairs #Ba54</t>
+          <t>Macarons #BX96</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -626,7 +626,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tarta de manzana #kL22</t>
+          <t>Tarta de manzana #ZR49</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Tarta de manzana #kL22</t>
+          <t>Tarta de manzana #ZR49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Tarta de manzana #kL22</t>
+          <t>Tarta de manzana #ZR49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -689,7 +689,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Tarta de manzana #kL22</t>
+          <t>Tarta de manzana #ZR49</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Éclairs #OB27</t>
+          <t>Galletas #mC49</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -731,7 +731,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Éclairs #OB27</t>
+          <t>Galletas #mC49</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Éclairs #OB27</t>
+          <t>Galletas #mC49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -773,7 +773,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Éclairs #OB27</t>
+          <t>Galletas #mC49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cheesecake #cO39</t>
+          <t>Brownies #zF70</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cheesecake #cO39</t>
+          <t>Brownies #zF70</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cheesecake #cO39</t>
+          <t>Brownies #zF70</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -857,7 +857,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cheesecake #cO39</t>
+          <t>Brownies #zF70</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brownies #Nw71</t>
+          <t>Tarta de manzana #Su38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brownies #Nw71</t>
+          <t>Tarta de manzana #Su38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -920,7 +920,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brownies #Nw71</t>
+          <t>Tarta de manzana #Su38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brownies #Nw71</t>
+          <t>Tarta de manzana #Su38</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -962,7 +962,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Galletas #Oe41</t>
+          <t>Donas #YN89</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -983,7 +983,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Galletas #Oe41</t>
+          <t>Donas #YN89</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1004,7 +1004,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Galletas #Oe41</t>
+          <t>Donas #YN89</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1025,7 +1025,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Galletas #Oe41</t>
+          <t>Donas #YN89</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cheesecake #GL16</t>
+          <t>Macarons #hR54</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1067,7 +1067,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cheesecake #GL16</t>
+          <t>Macarons #hR54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cheesecake #GL16</t>
+          <t>Macarons #hR54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1109,7 +1109,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cheesecake #GL16</t>
+          <t>Macarons #hR54</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1130,7 +1130,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cupcakes #Qp93</t>
+          <t>Macarons #Hj32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1151,7 +1151,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cupcakes #Qp93</t>
+          <t>Macarons #Hj32</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1172,7 +1172,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cupcakes #Qp93</t>
+          <t>Macarons #Hj32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cupcakes #Qp93</t>
+          <t>Macarons #Hj32</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1214,7 +1214,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cupcakes #pW89</t>
+          <t>Cheesecake #aO91</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1235,7 +1235,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cupcakes #pW89</t>
+          <t>Cheesecake #aO91</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cupcakes #pW89</t>
+          <t>Cheesecake #aO91</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cupcakes #pW89</t>
+          <t>Cheesecake #aO91</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1298,7 +1298,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Galletas #ox76</t>
+          <t>Brownies #NU72</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Galletas #ox76</t>
+          <t>Brownies #NU72</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1340,7 +1340,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Galletas #ox76</t>
+          <t>Brownies #NU72</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1361,7 +1361,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Galletas #ox76</t>
+          <t>Brownies #NU72</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Galletas #zW60</t>
+          <t>Macarons #mt49</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1403,7 +1403,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Galletas #zW60</t>
+          <t>Macarons #mt49</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Galletas #zW60</t>
+          <t>Macarons #mt49</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1445,7 +1445,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Galletas #zW60</t>
+          <t>Macarons #mt49</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Brownies #wQ81</t>
+          <t>Panetone #LH38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Brownies #wQ81</t>
+          <t>Panetone #LH38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1508,7 +1508,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Brownies #wQ81</t>
+          <t>Panetone #LH38</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Brownies #wQ81</t>
+          <t>Panetone #LH38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Panetone #ci72</t>
+          <t>Cheesecake #aV34</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Panetone #ci72</t>
+          <t>Cheesecake #aV34</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Panetone #ci72</t>
+          <t>Cheesecake #aV34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1613,7 +1613,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Panetone #ci72</t>
+          <t>Cheesecake #aV34</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1634,7 +1634,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Fw99</t>
+          <t>Brownies #Ix00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1655,7 +1655,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Fw99</t>
+          <t>Brownies #Ix00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1676,7 +1676,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Fw99</t>
+          <t>Brownies #Ix00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Fw99</t>
+          <t>Brownies #Ix00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1718,7 +1718,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cheesecake #hk55</t>
+          <t>Cheesecake #XT03</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1739,7 +1739,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cheesecake #hk55</t>
+          <t>Cheesecake #XT03</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cheesecake #hk55</t>
+          <t>Cheesecake #XT03</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1781,7 +1781,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cheesecake #hk55</t>
+          <t>Cheesecake #XT03</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1802,7 +1802,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Brownies #xb69</t>
+          <t>Panetone #oA28</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1823,7 +1823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Brownies #xb69</t>
+          <t>Panetone #oA28</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1844,7 +1844,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Brownies #xb69</t>
+          <t>Panetone #oA28</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1865,7 +1865,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Brownies #xb69</t>
+          <t>Panetone #oA28</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1886,7 +1886,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #DZ24</t>
+          <t>Panetone #DR97</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #DZ24</t>
+          <t>Panetone #DR97</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #DZ24</t>
+          <t>Panetone #DR97</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1949,7 +1949,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #DZ24</t>
+          <t>Panetone #DR97</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1970,7 +1970,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #WA15</t>
+          <t>Tarta de manzana #IT02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #WA15</t>
+          <t>Tarta de manzana #IT02</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2012,7 +2012,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #WA15</t>
+          <t>Tarta de manzana #IT02</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2033,7 +2033,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #WA15</t>
+          <t>Tarta de manzana #IT02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2054,7 +2054,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Brownies #fY80</t>
+          <t>Macarons #xC94</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Brownies #fY80</t>
+          <t>Macarons #xC94</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2096,7 +2096,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Brownies #fY80</t>
+          <t>Macarons #xC94</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Brownies #fY80</t>
+          <t>Macarons #xC94</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Panetone #qf54</t>
+          <t>Galletas #QA48</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Panetone #qf54</t>
+          <t>Galletas #QA48</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2180,7 +2180,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Panetone #qf54</t>
+          <t>Galletas #QA48</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2201,7 +2201,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Panetone #qf54</t>
+          <t>Galletas #QA48</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2222,7 +2222,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Galletas #XC94</t>
+          <t>Cupcakes #Zk48</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2243,7 +2243,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Galletas #XC94</t>
+          <t>Cupcakes #Zk48</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2264,7 +2264,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Galletas #XC94</t>
+          <t>Cupcakes #Zk48</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2285,7 +2285,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Galletas #XC94</t>
+          <t>Cupcakes #Zk48</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2306,7 +2306,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tarta de manzana #rx75</t>
+          <t>Brownies #cz71</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2327,7 +2327,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tarta de manzana #rx75</t>
+          <t>Brownies #cz71</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2348,7 +2348,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tarta de manzana #rx75</t>
+          <t>Brownies #cz71</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2369,7 +2369,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tarta de manzana #rx75</t>
+          <t>Brownies #cz71</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2390,7 +2390,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Vk20</t>
+          <t>Panetone #ln88</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2411,7 +2411,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Vk20</t>
+          <t>Panetone #ln88</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2432,7 +2432,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Vk20</t>
+          <t>Panetone #ln88</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2453,7 +2453,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Vk20</t>
+          <t>Panetone #ln88</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2474,7 +2474,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Macarons #BS98</t>
+          <t>Brownies #xP37</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2495,7 +2495,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Macarons #BS98</t>
+          <t>Brownies #xP37</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2516,7 +2516,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Macarons #BS98</t>
+          <t>Brownies #xP37</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2537,7 +2537,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Macarons #BS98</t>
+          <t>Brownies #xP37</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2558,7 +2558,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cupcakes #XW68</t>
+          <t>Donas #WJ23</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2579,7 +2579,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cupcakes #XW68</t>
+          <t>Donas #WJ23</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2600,7 +2600,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cupcakes #XW68</t>
+          <t>Donas #WJ23</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -2621,7 +2621,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cupcakes #XW68</t>
+          <t>Donas #WJ23</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -2642,7 +2642,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Galletas #mr04</t>
+          <t>Brownies #ru46</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2663,7 +2663,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Galletas #mr04</t>
+          <t>Brownies #ru46</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -2684,7 +2684,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Galletas #mr04</t>
+          <t>Brownies #ru46</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -2705,7 +2705,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Galletas #mr04</t>
+          <t>Brownies #ru46</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -2726,7 +2726,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #pU22</t>
+          <t>Cupcakes #Rw25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -2747,7 +2747,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #pU22</t>
+          <t>Cupcakes #Rw25</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -2768,7 +2768,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #pU22</t>
+          <t>Cupcakes #Rw25</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -2789,7 +2789,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #pU22</t>
+          <t>Cupcakes #Rw25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -2810,7 +2810,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Galletas #Jn27</t>
+          <t>Cupcakes #ZT34</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2831,7 +2831,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Galletas #Jn27</t>
+          <t>Cupcakes #ZT34</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2852,7 +2852,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Galletas #Jn27</t>
+          <t>Cupcakes #ZT34</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2873,7 +2873,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Galletas #Jn27</t>
+          <t>Cupcakes #ZT34</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -2894,7 +2894,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Panetone #GE92</t>
+          <t>Tarta de manzana #Vo04</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -2915,7 +2915,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Panetone #GE92</t>
+          <t>Tarta de manzana #Vo04</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -2936,7 +2936,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Panetone #GE92</t>
+          <t>Tarta de manzana #Vo04</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -2957,7 +2957,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Panetone #GE92</t>
+          <t>Tarta de manzana #Vo04</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -2978,7 +2978,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Galletas #Di10</t>
+          <t>Donas #tT78</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -2999,7 +2999,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Galletas #Di10</t>
+          <t>Donas #tT78</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3020,7 +3020,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Galletas #Di10</t>
+          <t>Donas #tT78</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3041,7 +3041,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Galletas #Di10</t>
+          <t>Donas #tT78</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Tarta de manzana #cw94</t>
+          <t>Panetone #ua28</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3083,7 +3083,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Tarta de manzana #cw94</t>
+          <t>Panetone #ua28</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3104,7 +3104,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Tarta de manzana #cw94</t>
+          <t>Panetone #ua28</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3125,7 +3125,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tarta de manzana #cw94</t>
+          <t>Panetone #ua28</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Galletas #JJ30</t>
+          <t>Panetone #vr84</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3167,7 +3167,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Galletas #JJ30</t>
+          <t>Panetone #vr84</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3188,7 +3188,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Galletas #JJ30</t>
+          <t>Panetone #vr84</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3209,7 +3209,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Galletas #JJ30</t>
+          <t>Panetone #vr84</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3230,7 +3230,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Donas #Fb15</t>
+          <t>Cheesecake #YJ39</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3251,7 +3251,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Donas #Fb15</t>
+          <t>Cheesecake #YJ39</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3272,7 +3272,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Donas #Fb15</t>
+          <t>Cheesecake #YJ39</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3293,7 +3293,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Donas #Fb15</t>
+          <t>Cheesecake #YJ39</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3314,7 +3314,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Tarta de manzana #wI09</t>
+          <t>Galletas #RO51</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3335,7 +3335,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Tarta de manzana #wI09</t>
+          <t>Galletas #RO51</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3356,7 +3356,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Tarta de manzana #wI09</t>
+          <t>Galletas #RO51</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3377,7 +3377,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Tarta de manzana #wI09</t>
+          <t>Galletas #RO51</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3398,7 +3398,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cupcakes #kT62</t>
+          <t>Pastel de chocolate #sj35</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3419,7 +3419,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cupcakes #kT62</t>
+          <t>Pastel de chocolate #sj35</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3440,7 +3440,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Cupcakes #kT62</t>
+          <t>Pastel de chocolate #sj35</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3461,7 +3461,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cupcakes #kT62</t>
+          <t>Pastel de chocolate #sj35</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3482,7 +3482,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Tarta de manzana #ez79</t>
+          <t>Tarta de manzana #Fr58</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3503,7 +3503,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Tarta de manzana #ez79</t>
+          <t>Tarta de manzana #Fr58</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3524,7 +3524,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Tarta de manzana #ez79</t>
+          <t>Tarta de manzana #Fr58</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3545,7 +3545,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Tarta de manzana #ez79</t>
+          <t>Tarta de manzana #Fr58</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3566,7 +3566,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #RY20</t>
+          <t>Cupcakes #ad67</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3587,7 +3587,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #RY20</t>
+          <t>Cupcakes #ad67</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3608,7 +3608,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #RY20</t>
+          <t>Cupcakes #ad67</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #RY20</t>
+          <t>Cupcakes #ad67</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3650,7 +3650,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Cheesecake #DC17</t>
+          <t>Macarons #ZZ13</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3671,7 +3671,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Cheesecake #DC17</t>
+          <t>Macarons #ZZ13</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3692,7 +3692,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Cheesecake #DC17</t>
+          <t>Macarons #ZZ13</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3713,7 +3713,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Cheesecake #DC17</t>
+          <t>Macarons #ZZ13</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -3734,7 +3734,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Brownies #uD93</t>
+          <t>Pastel de chocolate #od94</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3755,7 +3755,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Brownies #uD93</t>
+          <t>Pastel de chocolate #od94</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3776,7 +3776,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Brownies #uD93</t>
+          <t>Pastel de chocolate #od94</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -3797,7 +3797,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Brownies #uD93</t>
+          <t>Pastel de chocolate #od94</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3818,7 +3818,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Cheesecake #eA13</t>
+          <t>Tarta de manzana #mZ82</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3839,7 +3839,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Cheesecake #eA13</t>
+          <t>Tarta de manzana #mZ82</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3860,7 +3860,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Cheesecake #eA13</t>
+          <t>Tarta de manzana #mZ82</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -3881,7 +3881,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Cheesecake #eA13</t>
+          <t>Tarta de manzana #mZ82</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -3902,7 +3902,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Panetone #od77</t>
+          <t>Tarta de manzana #gx46</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3923,7 +3923,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Panetone #od77</t>
+          <t>Tarta de manzana #gx46</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3944,7 +3944,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Panetone #od77</t>
+          <t>Tarta de manzana #gx46</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3965,7 +3965,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Panetone #od77</t>
+          <t>Tarta de manzana #gx46</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Cupcakes #qd08</t>
+          <t>Brownies #Pa33</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4007,7 +4007,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Cupcakes #qd08</t>
+          <t>Brownies #Pa33</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4028,7 +4028,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Cupcakes #qd08</t>
+          <t>Brownies #Pa33</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4049,7 +4049,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Cupcakes #qd08</t>
+          <t>Brownies #Pa33</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4070,7 +4070,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Éclairs #Fg54</t>
+          <t>Éclairs #Qq12</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4091,7 +4091,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Éclairs #Fg54</t>
+          <t>Éclairs #Qq12</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4112,7 +4112,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Éclairs #Fg54</t>
+          <t>Éclairs #Qq12</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4133,7 +4133,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Éclairs #Fg54</t>
+          <t>Éclairs #Qq12</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4154,7 +4154,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Donas #Gy02</t>
+          <t>Cheesecake #Vt11</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4175,7 +4175,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Donas #Gy02</t>
+          <t>Cheesecake #Vt11</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Donas #Gy02</t>
+          <t>Cheesecake #Vt11</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4217,7 +4217,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Donas #Gy02</t>
+          <t>Cheesecake #Vt11</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4238,7 +4238,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Brownies #Dk28</t>
+          <t>Brownies #KS39</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4259,7 +4259,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Brownies #Dk28</t>
+          <t>Brownies #KS39</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4280,7 +4280,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Brownies #Dk28</t>
+          <t>Brownies #KS39</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4301,7 +4301,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Brownies #Dk28</t>
+          <t>Brownies #KS39</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4322,7 +4322,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Xr82</t>
+          <t>Galletas #YN57</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Xr82</t>
+          <t>Galletas #YN57</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4364,7 +4364,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Xr82</t>
+          <t>Galletas #YN57</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4385,7 +4385,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Xr82</t>
+          <t>Galletas #YN57</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4406,7 +4406,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Cheesecake #Px86</t>
+          <t>Cupcakes #wA52</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4427,7 +4427,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Cheesecake #Px86</t>
+          <t>Cupcakes #wA52</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4448,7 +4448,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Cheesecake #Px86</t>
+          <t>Cupcakes #wA52</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4469,7 +4469,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Cheesecake #Px86</t>
+          <t>Cupcakes #wA52</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4490,7 +4490,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #tT69</t>
+          <t>Macarons #fs60</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4511,7 +4511,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #tT69</t>
+          <t>Macarons #fs60</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4532,7 +4532,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #tT69</t>
+          <t>Macarons #fs60</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4553,7 +4553,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #tT69</t>
+          <t>Macarons #fs60</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4574,7 +4574,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Macarons #Mu26</t>
+          <t>Éclairs #lX61</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4595,7 +4595,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Macarons #Mu26</t>
+          <t>Éclairs #lX61</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4616,7 +4616,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Macarons #Mu26</t>
+          <t>Éclairs #lX61</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4637,7 +4637,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Macarons #Mu26</t>
+          <t>Éclairs #lX61</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Brownies #xx92</t>
+          <t>Cupcakes #LJ41</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4679,7 +4679,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Brownies #xx92</t>
+          <t>Cupcakes #LJ41</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Brownies #xx92</t>
+          <t>Cupcakes #LJ41</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4721,7 +4721,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Brownies #xx92</t>
+          <t>Cupcakes #LJ41</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4742,7 +4742,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Tarta de manzana #JR43</t>
+          <t>Galletas #Pc05</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4763,7 +4763,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Tarta de manzana #JR43</t>
+          <t>Galletas #Pc05</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4784,7 +4784,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Tarta de manzana #JR43</t>
+          <t>Galletas #Pc05</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4805,7 +4805,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Tarta de manzana #JR43</t>
+          <t>Galletas #Pc05</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4826,7 +4826,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #wK04</t>
+          <t>Tarta de manzana #Tx60</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4847,7 +4847,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #wK04</t>
+          <t>Tarta de manzana #Tx60</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4868,7 +4868,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #wK04</t>
+          <t>Tarta de manzana #Tx60</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4889,7 +4889,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #wK04</t>
+          <t>Tarta de manzana #Tx60</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4910,7 +4910,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Éclairs #pG80</t>
+          <t>Cupcakes #AZ22</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4931,7 +4931,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Éclairs #pG80</t>
+          <t>Cupcakes #AZ22</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -4952,7 +4952,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Éclairs #pG80</t>
+          <t>Cupcakes #AZ22</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4973,7 +4973,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Éclairs #pG80</t>
+          <t>Cupcakes #AZ22</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -4994,7 +4994,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Éclairs #Pz41</t>
+          <t>Pastel de chocolate #xS75</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Éclairs #Pz41</t>
+          <t>Pastel de chocolate #xS75</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5036,7 +5036,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Éclairs #Pz41</t>
+          <t>Pastel de chocolate #xS75</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Éclairs #Pz41</t>
+          <t>Pastel de chocolate #xS75</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5078,7 +5078,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #wE19</t>
+          <t>Tarta de manzana #ET43</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #wE19</t>
+          <t>Tarta de manzana #ET43</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5120,7 +5120,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #wE19</t>
+          <t>Tarta de manzana #ET43</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5141,7 +5141,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #wE19</t>
+          <t>Tarta de manzana #ET43</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5162,7 +5162,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Rh22</t>
+          <t>Macarons #xR27</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5183,7 +5183,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Rh22</t>
+          <t>Macarons #xR27</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5204,7 +5204,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Rh22</t>
+          <t>Macarons #xR27</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5225,7 +5225,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Rh22</t>
+          <t>Macarons #xR27</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5246,7 +5246,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Brownies #XK57</t>
+          <t>Cheesecake #iZ34</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5267,7 +5267,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Brownies #XK57</t>
+          <t>Cheesecake #iZ34</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5288,7 +5288,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Brownies #XK57</t>
+          <t>Cheesecake #iZ34</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5309,7 +5309,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Brownies #XK57</t>
+          <t>Cheesecake #iZ34</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5330,7 +5330,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Cheesecake #RQ65</t>
+          <t>Panetone #Rs42</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5351,7 +5351,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Cheesecake #RQ65</t>
+          <t>Panetone #Rs42</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5372,7 +5372,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Cheesecake #RQ65</t>
+          <t>Panetone #Rs42</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5393,7 +5393,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Cheesecake #RQ65</t>
+          <t>Panetone #Rs42</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5414,7 +5414,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Tarta de manzana #vN61</t>
+          <t>Pastel de chocolate #EH07</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5435,7 +5435,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Tarta de manzana #vN61</t>
+          <t>Pastel de chocolate #EH07</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5456,7 +5456,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Tarta de manzana #vN61</t>
+          <t>Pastel de chocolate #EH07</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5477,7 +5477,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Tarta de manzana #vN61</t>
+          <t>Pastel de chocolate #EH07</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5498,7 +5498,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Cheesecake #We95</t>
+          <t>Galletas #Rh48</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Cheesecake #We95</t>
+          <t>Galletas #Rh48</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5540,7 +5540,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Cheesecake #We95</t>
+          <t>Galletas #Rh48</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5561,7 +5561,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Cheesecake #We95</t>
+          <t>Galletas #Rh48</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5582,7 +5582,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Donas #GK84</t>
+          <t>Galletas #Ug28</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Donas #GK84</t>
+          <t>Galletas #Ug28</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5624,7 +5624,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Donas #GK84</t>
+          <t>Galletas #Ug28</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5645,7 +5645,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Donas #GK84</t>
+          <t>Galletas #Ug28</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5666,7 +5666,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Éclairs #TM07</t>
+          <t>Tarta de manzana #if91</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5687,7 +5687,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Éclairs #TM07</t>
+          <t>Tarta de manzana #if91</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5708,7 +5708,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Éclairs #TM07</t>
+          <t>Tarta de manzana #if91</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5729,7 +5729,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Éclairs #TM07</t>
+          <t>Tarta de manzana #if91</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5750,7 +5750,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Éclairs #GJ06</t>
+          <t>Brownies #MP07</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Éclairs #GJ06</t>
+          <t>Brownies #MP07</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5792,7 +5792,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Éclairs #GJ06</t>
+          <t>Brownies #MP07</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5813,7 +5813,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Éclairs #GJ06</t>
+          <t>Brownies #MP07</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -5834,7 +5834,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Macarons #ET65</t>
+          <t>Brownies #zV81</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -5855,7 +5855,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Macarons #ET65</t>
+          <t>Brownies #zV81</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -5876,7 +5876,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Macarons #ET65</t>
+          <t>Brownies #zV81</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -5897,7 +5897,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Macarons #ET65</t>
+          <t>Brownies #zV81</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -5918,7 +5918,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Panetone #wE96</t>
+          <t>Brownies #rs73</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -5939,7 +5939,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Panetone #wE96</t>
+          <t>Brownies #rs73</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -5960,7 +5960,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Panetone #wE96</t>
+          <t>Brownies #rs73</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -5981,7 +5981,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Panetone #wE96</t>
+          <t>Brownies #rs73</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Macarons #vm40</t>
+          <t>Pastel de chocolate #Hn87</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6023,7 +6023,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Macarons #vm40</t>
+          <t>Pastel de chocolate #Hn87</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6044,7 +6044,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Macarons #vm40</t>
+          <t>Pastel de chocolate #Hn87</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6065,7 +6065,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Macarons #vm40</t>
+          <t>Pastel de chocolate #Hn87</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6086,7 +6086,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Brownies #dP88</t>
+          <t>Cupcakes #iq78</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6107,7 +6107,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Brownies #dP88</t>
+          <t>Cupcakes #iq78</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6128,7 +6128,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Brownies #dP88</t>
+          <t>Cupcakes #iq78</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6149,7 +6149,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Brownies #dP88</t>
+          <t>Cupcakes #iq78</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6170,7 +6170,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #gb88</t>
+          <t>Cheesecake #ts79</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6191,7 +6191,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #gb88</t>
+          <t>Cheesecake #ts79</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6212,7 +6212,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #gb88</t>
+          <t>Cheesecake #ts79</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #gb88</t>
+          <t>Cheesecake #ts79</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6254,7 +6254,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Ul31</t>
+          <t>Cupcakes #PG51</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6275,7 +6275,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Ul31</t>
+          <t>Cupcakes #PG51</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6296,7 +6296,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Ul31</t>
+          <t>Cupcakes #PG51</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6317,7 +6317,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Ul31</t>
+          <t>Cupcakes #PG51</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6338,7 +6338,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Cupcakes #og53</t>
+          <t>Éclairs #Pc74</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6359,7 +6359,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Cupcakes #og53</t>
+          <t>Éclairs #Pc74</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6380,7 +6380,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Cupcakes #og53</t>
+          <t>Éclairs #Pc74</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6401,7 +6401,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Cupcakes #og53</t>
+          <t>Éclairs #Pc74</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6422,7 +6422,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Cupcakes #WR90</t>
+          <t>Pastel de chocolate #eF52</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6443,7 +6443,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Cupcakes #WR90</t>
+          <t>Pastel de chocolate #eF52</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6464,7 +6464,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Cupcakes #WR90</t>
+          <t>Pastel de chocolate #eF52</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6485,7 +6485,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Cupcakes #WR90</t>
+          <t>Pastel de chocolate #eF52</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6506,7 +6506,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Éclairs #qM19</t>
+          <t>Tarta de manzana #kL19</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6527,7 +6527,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Éclairs #qM19</t>
+          <t>Tarta de manzana #kL19</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6548,7 +6548,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Éclairs #qM19</t>
+          <t>Tarta de manzana #kL19</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6569,7 +6569,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Éclairs #qM19</t>
+          <t>Tarta de manzana #kL19</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6590,7 +6590,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Macarons #ce51</t>
+          <t>Éclairs #zH03</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6611,7 +6611,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Macarons #ce51</t>
+          <t>Éclairs #zH03</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6632,7 +6632,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Macarons #ce51</t>
+          <t>Éclairs #zH03</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6653,7 +6653,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Macarons #ce51</t>
+          <t>Éclairs #zH03</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6674,7 +6674,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Cheesecake #PY79</t>
+          <t>Donas #oM52</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6695,7 +6695,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Cheesecake #PY79</t>
+          <t>Donas #oM52</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6716,7 +6716,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Cheesecake #PY79</t>
+          <t>Donas #oM52</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6737,7 +6737,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Cheesecake #PY79</t>
+          <t>Donas #oM52</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6758,7 +6758,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Sf85</t>
+          <t>Pastel de chocolate #lm89</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6779,7 +6779,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Sf85</t>
+          <t>Pastel de chocolate #lm89</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -6800,7 +6800,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Sf85</t>
+          <t>Pastel de chocolate #lm89</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6821,7 +6821,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Sf85</t>
+          <t>Pastel de chocolate #lm89</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -6842,7 +6842,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Macarons #lu38</t>
+          <t>Cupcakes #XF12</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -6863,7 +6863,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Macarons #lu38</t>
+          <t>Cupcakes #XF12</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -6884,7 +6884,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Macarons #lu38</t>
+          <t>Cupcakes #XF12</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -6905,7 +6905,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Macarons #lu38</t>
+          <t>Cupcakes #XF12</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -6926,7 +6926,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Tarta de manzana #VF69</t>
+          <t>Macarons #IW43</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -6947,7 +6947,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Tarta de manzana #VF69</t>
+          <t>Macarons #IW43</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -6968,7 +6968,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Tarta de manzana #VF69</t>
+          <t>Macarons #IW43</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -6989,7 +6989,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Tarta de manzana #VF69</t>
+          <t>Macarons #IW43</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7010,7 +7010,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Galletas #JA79</t>
+          <t>Cupcakes #qp17</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Galletas #JA79</t>
+          <t>Cupcakes #qp17</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7052,7 +7052,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Galletas #JA79</t>
+          <t>Cupcakes #qp17</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7073,7 +7073,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Galletas #JA79</t>
+          <t>Cupcakes #qp17</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7094,7 +7094,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Cheesecake #oA37</t>
+          <t>Panetone #AC85</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7115,7 +7115,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Cheesecake #oA37</t>
+          <t>Panetone #AC85</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7136,7 +7136,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Cheesecake #oA37</t>
+          <t>Panetone #AC85</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7157,7 +7157,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Cheesecake #oA37</t>
+          <t>Panetone #AC85</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7178,7 +7178,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Tarta de manzana #WL39</t>
+          <t>Panetone #XD47</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7199,7 +7199,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Tarta de manzana #WL39</t>
+          <t>Panetone #XD47</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7220,7 +7220,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Tarta de manzana #WL39</t>
+          <t>Panetone #XD47</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7241,7 +7241,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Tarta de manzana #WL39</t>
+          <t>Panetone #XD47</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7262,7 +7262,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Macarons #KP39</t>
+          <t>Tarta de manzana #tP89</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7283,7 +7283,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Macarons #KP39</t>
+          <t>Tarta de manzana #tP89</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7304,7 +7304,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Macarons #KP39</t>
+          <t>Tarta de manzana #tP89</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7325,7 +7325,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Macarons #KP39</t>
+          <t>Tarta de manzana #tP89</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7346,7 +7346,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Brownies #RO97</t>
+          <t>Tarta de manzana #kH39</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7367,7 +7367,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Brownies #RO97</t>
+          <t>Tarta de manzana #kH39</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7388,7 +7388,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Brownies #RO97</t>
+          <t>Tarta de manzana #kH39</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7409,7 +7409,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Brownies #RO97</t>
+          <t>Tarta de manzana #kH39</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -7430,7 +7430,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Donas #FF72</t>
+          <t>Galletas #Wl08</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7451,7 +7451,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Donas #FF72</t>
+          <t>Galletas #Wl08</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -7472,7 +7472,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Donas #FF72</t>
+          <t>Galletas #Wl08</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7493,7 +7493,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Donas #FF72</t>
+          <t>Galletas #Wl08</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7514,7 +7514,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Galletas #ux22</t>
+          <t>Macarons #za75</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7535,7 +7535,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Galletas #ux22</t>
+          <t>Macarons #za75</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7556,7 +7556,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Galletas #ux22</t>
+          <t>Macarons #za75</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7577,7 +7577,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Galletas #ux22</t>
+          <t>Macarons #za75</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7598,7 +7598,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Éclairs #vR98</t>
+          <t>Panetone #pn52</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7619,7 +7619,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Éclairs #vR98</t>
+          <t>Panetone #pn52</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Éclairs #vR98</t>
+          <t>Panetone #pn52</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -7661,7 +7661,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Éclairs #vR98</t>
+          <t>Panetone #pn52</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -7682,7 +7682,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Donas #eI10</t>
+          <t>Panetone #cl41</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7703,7 +7703,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Donas #eI10</t>
+          <t>Panetone #cl41</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -7724,7 +7724,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Donas #eI10</t>
+          <t>Panetone #cl41</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -7745,7 +7745,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Donas #eI10</t>
+          <t>Panetone #cl41</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Panetone #qG53</t>
+          <t>Cheesecake #Ly96</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -7787,7 +7787,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Panetone #qG53</t>
+          <t>Cheesecake #Ly96</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -7808,7 +7808,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Panetone #qG53</t>
+          <t>Cheesecake #Ly96</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -7829,7 +7829,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Panetone #qG53</t>
+          <t>Cheesecake #Ly96</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -7850,7 +7850,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Cupcakes #Nt91</t>
+          <t>Panetone #BU91</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -7871,7 +7871,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Cupcakes #Nt91</t>
+          <t>Panetone #BU91</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -7892,7 +7892,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Cupcakes #Nt91</t>
+          <t>Panetone #BU91</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -7913,7 +7913,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Cupcakes #Nt91</t>
+          <t>Panetone #BU91</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #oH06</t>
+          <t>Cupcakes #Fp00</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -7955,7 +7955,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #oH06</t>
+          <t>Cupcakes #Fp00</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -7976,7 +7976,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #oH06</t>
+          <t>Cupcakes #Fp00</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -7997,7 +7997,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #oH06</t>
+          <t>Cupcakes #Fp00</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -8018,7 +8018,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Donas #zk15</t>
+          <t>Brownies #Zm83</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8039,7 +8039,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Donas #zk15</t>
+          <t>Brownies #Zm83</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8060,7 +8060,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Donas #zk15</t>
+          <t>Brownies #Zm83</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -8081,7 +8081,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Donas #zk15</t>
+          <t>Brownies #Zm83</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8102,7 +8102,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Cupcakes #MC61</t>
+          <t>Pastel de chocolate #uL73</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Cupcakes #MC61</t>
+          <t>Pastel de chocolate #uL73</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -8144,7 +8144,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Cupcakes #MC61</t>
+          <t>Pastel de chocolate #uL73</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -8165,7 +8165,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Cupcakes #MC61</t>
+          <t>Pastel de chocolate #uL73</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -8186,7 +8186,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Cupcakes #HC46</t>
+          <t>Donas #gI59</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -8207,7 +8207,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Cupcakes #HC46</t>
+          <t>Donas #gI59</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -8228,7 +8228,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Cupcakes #HC46</t>
+          <t>Donas #gI59</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -8249,7 +8249,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Cupcakes #HC46</t>
+          <t>Donas #gI59</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -8270,7 +8270,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Brownies #Bx77</t>
+          <t>Galletas #Ze79</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -8291,7 +8291,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Brownies #Bx77</t>
+          <t>Galletas #Ze79</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -8312,7 +8312,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Brownies #Bx77</t>
+          <t>Galletas #Ze79</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -8333,7 +8333,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Brownies #Bx77</t>
+          <t>Galletas #Ze79</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -8354,7 +8354,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #sA41</t>
+          <t>Macarons #Rz87</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -8375,7 +8375,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #sA41</t>
+          <t>Macarons #Rz87</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -8396,7 +8396,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #sA41</t>
+          <t>Macarons #Rz87</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -8417,7 +8417,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #sA41</t>
+          <t>Macarons #Rz87</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -8438,7 +8438,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Tarta de manzana #bz21</t>
+          <t>Cheesecake #fM74</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -8459,7 +8459,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Tarta de manzana #bz21</t>
+          <t>Cheesecake #fM74</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -8480,7 +8480,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Tarta de manzana #bz21</t>
+          <t>Cheesecake #fM74</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -8501,7 +8501,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Tarta de manzana #bz21</t>
+          <t>Cheesecake #fM74</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -8522,7 +8522,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Donas #sy23</t>
+          <t>Panetone #Dh82</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -8543,7 +8543,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Donas #sy23</t>
+          <t>Panetone #Dh82</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -8564,7 +8564,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Donas #sy23</t>
+          <t>Panetone #Dh82</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -8585,7 +8585,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Donas #sy23</t>
+          <t>Panetone #Dh82</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -8606,7 +8606,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Cupcakes #wh64</t>
+          <t>Panetone #tc31</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -8627,7 +8627,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Cupcakes #wh64</t>
+          <t>Panetone #tc31</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -8648,7 +8648,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Cupcakes #wh64</t>
+          <t>Panetone #tc31</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Cupcakes #wh64</t>
+          <t>Panetone #tc31</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -8690,7 +8690,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Brownies #ND71</t>
+          <t>Brownies #qG04</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -8711,7 +8711,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Brownies #ND71</t>
+          <t>Brownies #qG04</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -8732,7 +8732,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Brownies #ND71</t>
+          <t>Brownies #qG04</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -8753,7 +8753,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Brownies #ND71</t>
+          <t>Brownies #qG04</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -8774,7 +8774,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Macarons #KS03</t>
+          <t>Galletas #ZG82</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -8795,7 +8795,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Macarons #KS03</t>
+          <t>Galletas #ZG82</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -8816,7 +8816,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Macarons #KS03</t>
+          <t>Galletas #ZG82</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -8837,7 +8837,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Macarons #KS03</t>
+          <t>Galletas #ZG82</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -8858,7 +8858,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Macarons #Yr63</t>
+          <t>Panetone #nG62</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -8879,7 +8879,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Macarons #Yr63</t>
+          <t>Panetone #nG62</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -8900,7 +8900,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Macarons #Yr63</t>
+          <t>Panetone #nG62</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -8921,7 +8921,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Macarons #Yr63</t>
+          <t>Panetone #nG62</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -8942,7 +8942,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Macarons #ug38</t>
+          <t>Cheesecake #jq59</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -8963,7 +8963,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Macarons #ug38</t>
+          <t>Cheesecake #jq59</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -8984,7 +8984,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Macarons #ug38</t>
+          <t>Cheesecake #jq59</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -9005,7 +9005,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Macarons #ug38</t>
+          <t>Cheesecake #jq59</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -9026,7 +9026,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Macarons #gV08</t>
+          <t>Donas #Wh94</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -9047,7 +9047,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Macarons #gV08</t>
+          <t>Donas #Wh94</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -9068,7 +9068,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Macarons #gV08</t>
+          <t>Donas #Wh94</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -9089,7 +9089,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Macarons #gV08</t>
+          <t>Donas #Wh94</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -9110,7 +9110,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Brownies #Dg58</t>
+          <t>Donas #oP92</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -9131,7 +9131,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Brownies #Dg58</t>
+          <t>Donas #oP92</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -9152,7 +9152,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Brownies #Dg58</t>
+          <t>Donas #oP92</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -9173,7 +9173,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Brownies #Dg58</t>
+          <t>Donas #oP92</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -9194,7 +9194,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Éclairs #Gy94</t>
+          <t>Panetone #Vi48</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -9215,7 +9215,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Éclairs #Gy94</t>
+          <t>Panetone #Vi48</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -9236,7 +9236,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Éclairs #Gy94</t>
+          <t>Panetone #Vi48</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -9257,7 +9257,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Éclairs #Gy94</t>
+          <t>Panetone #Vi48</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -9278,7 +9278,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Tarta de manzana #pu26</t>
+          <t>Brownies #aS84</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -9299,7 +9299,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Tarta de manzana #pu26</t>
+          <t>Brownies #aS84</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -9320,7 +9320,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Tarta de manzana #pu26</t>
+          <t>Brownies #aS84</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -9341,7 +9341,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Tarta de manzana #pu26</t>
+          <t>Brownies #aS84</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -9362,7 +9362,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Tarta de manzana #AN20</t>
+          <t>Éclairs #PD95</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -9383,7 +9383,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Tarta de manzana #AN20</t>
+          <t>Éclairs #PD95</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -9404,7 +9404,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Tarta de manzana #AN20</t>
+          <t>Éclairs #PD95</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -9425,7 +9425,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Tarta de manzana #AN20</t>
+          <t>Éclairs #PD95</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Galletas #sp16</t>
+          <t>Cheesecake #Cf39</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -9467,7 +9467,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Galletas #sp16</t>
+          <t>Cheesecake #Cf39</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -9488,7 +9488,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Galletas #sp16</t>
+          <t>Cheesecake #Cf39</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -9509,7 +9509,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Galletas #sp16</t>
+          <t>Cheesecake #Cf39</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -9530,7 +9530,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Cheesecake #Yp27</t>
+          <t>Pastel de chocolate #jK52</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -9551,7 +9551,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Cheesecake #Yp27</t>
+          <t>Pastel de chocolate #jK52</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -9572,7 +9572,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Cheesecake #Yp27</t>
+          <t>Pastel de chocolate #jK52</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -9593,7 +9593,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Cheesecake #Yp27</t>
+          <t>Pastel de chocolate #jK52</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -9614,7 +9614,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Ha49</t>
+          <t>Cheesecake #Uh15</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -9635,7 +9635,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Ha49</t>
+          <t>Cheesecake #Uh15</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -9656,7 +9656,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Ha49</t>
+          <t>Cheesecake #Uh15</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -9677,7 +9677,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Ha49</t>
+          <t>Cheesecake #Uh15</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -9698,7 +9698,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Cupcakes #qZ72</t>
+          <t>Cheesecake #CG01</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -9719,7 +9719,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Cupcakes #qZ72</t>
+          <t>Cheesecake #CG01</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -9740,7 +9740,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Cupcakes #qZ72</t>
+          <t>Cheesecake #CG01</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -9761,7 +9761,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Cupcakes #qZ72</t>
+          <t>Cheesecake #CG01</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -9782,7 +9782,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Galletas #zQ67</t>
+          <t>Cheesecake #qh86</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -9803,7 +9803,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Galletas #zQ67</t>
+          <t>Cheesecake #qh86</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -9824,7 +9824,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Galletas #zQ67</t>
+          <t>Cheesecake #qh86</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -9845,7 +9845,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Galletas #zQ67</t>
+          <t>Cheesecake #qh86</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -9866,7 +9866,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #uf72</t>
+          <t>Macarons #VA88</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -9887,7 +9887,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #uf72</t>
+          <t>Macarons #VA88</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -9908,7 +9908,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #uf72</t>
+          <t>Macarons #VA88</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -9929,7 +9929,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #uf72</t>
+          <t>Macarons #VA88</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -9950,7 +9950,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Cupcakes #sf94</t>
+          <t>Tarta de manzana #JS61</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -9971,7 +9971,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Cupcakes #sf94</t>
+          <t>Tarta de manzana #JS61</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -9992,7 +9992,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Cupcakes #sf94</t>
+          <t>Tarta de manzana #JS61</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -10013,7 +10013,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Cupcakes #sf94</t>
+          <t>Tarta de manzana #JS61</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -10034,7 +10034,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Donas #kW69</t>
+          <t>Panetone #Qx15</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -10055,7 +10055,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Donas #kW69</t>
+          <t>Panetone #Qx15</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -10076,7 +10076,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Donas #kW69</t>
+          <t>Panetone #Qx15</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -10097,7 +10097,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Donas #kW69</t>
+          <t>Panetone #Qx15</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -10118,7 +10118,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #iQ20</t>
+          <t>Tarta de manzana #eb43</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -10139,7 +10139,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #iQ20</t>
+          <t>Tarta de manzana #eb43</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -10160,7 +10160,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #iQ20</t>
+          <t>Tarta de manzana #eb43</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -10181,7 +10181,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #iQ20</t>
+          <t>Tarta de manzana #eb43</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -10202,7 +10202,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Panetone #Zr29</t>
+          <t>Tarta de manzana #Mq78</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -10223,7 +10223,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Panetone #Zr29</t>
+          <t>Tarta de manzana #Mq78</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -10244,7 +10244,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Panetone #Zr29</t>
+          <t>Tarta de manzana #Mq78</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -10265,7 +10265,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Panetone #Zr29</t>
+          <t>Tarta de manzana #Mq78</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -10286,7 +10286,7 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Galletas #PQ43</t>
+          <t>Panetone #jr25</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -10307,7 +10307,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Galletas #PQ43</t>
+          <t>Panetone #jr25</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -10328,7 +10328,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Galletas #PQ43</t>
+          <t>Panetone #jr25</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -10349,7 +10349,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Galletas #PQ43</t>
+          <t>Panetone #jr25</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -10370,7 +10370,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Pq05</t>
+          <t>Galletas #JQ11</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -10391,7 +10391,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Pq05</t>
+          <t>Galletas #JQ11</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -10412,7 +10412,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Pq05</t>
+          <t>Galletas #JQ11</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -10433,7 +10433,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Pq05</t>
+          <t>Galletas #JQ11</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -10454,7 +10454,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Cheesecake #XZ71</t>
+          <t>Éclairs #kr67</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -10475,7 +10475,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Cheesecake #XZ71</t>
+          <t>Éclairs #kr67</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -10496,7 +10496,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Cheesecake #XZ71</t>
+          <t>Éclairs #kr67</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -10517,7 +10517,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Cheesecake #XZ71</t>
+          <t>Éclairs #kr67</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -10538,7 +10538,7 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Panetone #kg27</t>
+          <t>Cheesecake #bW97</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -10559,7 +10559,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Panetone #kg27</t>
+          <t>Cheesecake #bW97</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -10580,7 +10580,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Panetone #kg27</t>
+          <t>Cheesecake #bW97</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -10601,7 +10601,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Panetone #kg27</t>
+          <t>Cheesecake #bW97</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -10622,7 +10622,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #QS61</t>
+          <t>Cupcakes #sT76</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -10643,7 +10643,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #QS61</t>
+          <t>Cupcakes #sT76</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -10664,7 +10664,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #QS61</t>
+          <t>Cupcakes #sT76</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -10685,7 +10685,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #QS61</t>
+          <t>Cupcakes #sT76</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -10706,7 +10706,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Cupcakes #cE16</t>
+          <t>Pastel de chocolate #tV41</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -10727,7 +10727,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Cupcakes #cE16</t>
+          <t>Pastel de chocolate #tV41</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -10748,7 +10748,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Cupcakes #cE16</t>
+          <t>Pastel de chocolate #tV41</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -10769,7 +10769,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Cupcakes #cE16</t>
+          <t>Pastel de chocolate #tV41</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -10790,7 +10790,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Cheesecake #fh46</t>
+          <t>Tarta de manzana #cb11</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -10811,7 +10811,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Cheesecake #fh46</t>
+          <t>Tarta de manzana #cb11</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -10832,7 +10832,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Cheesecake #fh46</t>
+          <t>Tarta de manzana #cb11</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -10853,7 +10853,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Cheesecake #fh46</t>
+          <t>Tarta de manzana #cb11</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -10874,7 +10874,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Tarta de manzana #wq04</t>
+          <t>Cupcakes #lb38</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -10895,7 +10895,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Tarta de manzana #wq04</t>
+          <t>Cupcakes #lb38</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -10916,7 +10916,7 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Tarta de manzana #wq04</t>
+          <t>Cupcakes #lb38</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -10937,7 +10937,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Tarta de manzana #wq04</t>
+          <t>Cupcakes #lb38</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -10958,7 +10958,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Donas #UU59</t>
+          <t>Galletas #uI78</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Donas #UU59</t>
+          <t>Galletas #uI78</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -11000,7 +11000,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Donas #UU59</t>
+          <t>Galletas #uI78</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Donas #UU59</t>
+          <t>Galletas #uI78</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -11042,7 +11042,7 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Macarons #nw77</t>
+          <t>Galletas #Bi52</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -11063,7 +11063,7 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Macarons #nw77</t>
+          <t>Galletas #Bi52</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -11084,7 +11084,7 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Macarons #nw77</t>
+          <t>Galletas #Bi52</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -11105,7 +11105,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Macarons #nw77</t>
+          <t>Galletas #Bi52</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -11126,7 +11126,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Panetone #vK56</t>
+          <t>Éclairs #bo57</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -11147,7 +11147,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Panetone #vK56</t>
+          <t>Éclairs #bo57</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -11168,7 +11168,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Panetone #vK56</t>
+          <t>Éclairs #bo57</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -11189,7 +11189,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Panetone #vK56</t>
+          <t>Éclairs #bo57</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -11210,7 +11210,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Macarons #WK86</t>
+          <t>Donas #gv78</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -11231,7 +11231,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Macarons #WK86</t>
+          <t>Donas #gv78</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -11252,7 +11252,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Macarons #WK86</t>
+          <t>Donas #gv78</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -11273,7 +11273,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Macarons #WK86</t>
+          <t>Donas #gv78</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -11294,7 +11294,7 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Macarons #yE92</t>
+          <t>Galletas #Xe03</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -11315,7 +11315,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Macarons #yE92</t>
+          <t>Galletas #Xe03</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -11336,7 +11336,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Macarons #yE92</t>
+          <t>Galletas #Xe03</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -11357,7 +11357,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Macarons #yE92</t>
+          <t>Galletas #Xe03</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -11378,7 +11378,7 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Donas #TI23</t>
+          <t>Cupcakes #DV18</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -11399,7 +11399,7 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Donas #TI23</t>
+          <t>Cupcakes #DV18</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -11420,7 +11420,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Donas #TI23</t>
+          <t>Cupcakes #DV18</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -11441,7 +11441,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Donas #TI23</t>
+          <t>Cupcakes #DV18</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -11462,7 +11462,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Macarons #Ks22</t>
+          <t>Galletas #MN61</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -11483,7 +11483,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Macarons #Ks22</t>
+          <t>Galletas #MN61</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -11504,7 +11504,7 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Macarons #Ks22</t>
+          <t>Galletas #MN61</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -11525,7 +11525,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Macarons #Ks22</t>
+          <t>Galletas #MN61</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -11546,7 +11546,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Panetone #en41</t>
+          <t>Cheesecake #dj32</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -11567,7 +11567,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Panetone #en41</t>
+          <t>Cheesecake #dj32</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -11588,7 +11588,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Panetone #en41</t>
+          <t>Cheesecake #dj32</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -11609,7 +11609,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Panetone #en41</t>
+          <t>Cheesecake #dj32</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -11630,7 +11630,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Éclairs #YL79</t>
+          <t>Pastel de chocolate #sa14</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -11651,7 +11651,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Éclairs #YL79</t>
+          <t>Pastel de chocolate #sa14</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -11672,7 +11672,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Éclairs #YL79</t>
+          <t>Pastel de chocolate #sa14</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -11693,7 +11693,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Éclairs #YL79</t>
+          <t>Pastel de chocolate #sa14</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -11714,7 +11714,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Panetone #pe53</t>
+          <t>Panetone #bb58</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -11735,7 +11735,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Panetone #pe53</t>
+          <t>Panetone #bb58</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -11756,7 +11756,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Panetone #pe53</t>
+          <t>Panetone #bb58</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -11777,7 +11777,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Panetone #pe53</t>
+          <t>Panetone #bb58</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -11798,7 +11798,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Cupcakes #SF64</t>
+          <t>Tarta de manzana #Vs87</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -11819,7 +11819,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>Cupcakes #SF64</t>
+          <t>Tarta de manzana #Vs87</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -11840,7 +11840,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Cupcakes #SF64</t>
+          <t>Tarta de manzana #Vs87</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -11861,7 +11861,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Cupcakes #SF64</t>
+          <t>Tarta de manzana #Vs87</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -11882,7 +11882,7 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>Galletas #uN85</t>
+          <t>Donas #Ky07</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -11903,7 +11903,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Galletas #uN85</t>
+          <t>Donas #Ky07</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -11924,7 +11924,7 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Galletas #uN85</t>
+          <t>Donas #Ky07</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -11945,7 +11945,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Galletas #uN85</t>
+          <t>Donas #Ky07</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -11966,7 +11966,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Macarons #ue21</t>
+          <t>Cheesecake #hO96</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -11987,7 +11987,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Macarons #ue21</t>
+          <t>Cheesecake #hO96</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -12008,7 +12008,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Macarons #ue21</t>
+          <t>Cheesecake #hO96</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -12029,7 +12029,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Macarons #ue21</t>
+          <t>Cheesecake #hO96</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -12050,7 +12050,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Panetone #cP64</t>
+          <t>Cupcakes #Zb22</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -12071,7 +12071,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Panetone #cP64</t>
+          <t>Cupcakes #Zb22</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -12092,7 +12092,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Panetone #cP64</t>
+          <t>Cupcakes #Zb22</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -12113,7 +12113,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Panetone #cP64</t>
+          <t>Cupcakes #Zb22</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -12134,7 +12134,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Éclairs #kR32</t>
+          <t>Donas #KP85</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -12155,7 +12155,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Éclairs #kR32</t>
+          <t>Donas #KP85</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -12176,7 +12176,7 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Éclairs #kR32</t>
+          <t>Donas #KP85</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -12197,7 +12197,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Éclairs #kR32</t>
+          <t>Donas #KP85</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -12218,7 +12218,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Cupcakes #us85</t>
+          <t>Galletas #rM18</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -12239,7 +12239,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Cupcakes #us85</t>
+          <t>Galletas #rM18</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -12260,7 +12260,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Cupcakes #us85</t>
+          <t>Galletas #rM18</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -12281,7 +12281,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Cupcakes #us85</t>
+          <t>Galletas #rM18</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -12302,7 +12302,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Brownies #NW41</t>
+          <t>Pastel de chocolate #dx70</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -12323,7 +12323,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Brownies #NW41</t>
+          <t>Pastel de chocolate #dx70</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -12344,7 +12344,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Brownies #NW41</t>
+          <t>Pastel de chocolate #dx70</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -12365,7 +12365,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Brownies #NW41</t>
+          <t>Pastel de chocolate #dx70</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -12386,7 +12386,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Donas #mi20</t>
+          <t>Tarta de manzana #ZM54</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -12407,7 +12407,7 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Donas #mi20</t>
+          <t>Tarta de manzana #ZM54</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -12428,7 +12428,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Donas #mi20</t>
+          <t>Tarta de manzana #ZM54</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -12449,7 +12449,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Donas #mi20</t>
+          <t>Tarta de manzana #ZM54</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -12470,7 +12470,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Éclairs #dl65</t>
+          <t>Donas #Ga52</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -12491,7 +12491,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Éclairs #dl65</t>
+          <t>Donas #Ga52</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -12512,7 +12512,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Éclairs #dl65</t>
+          <t>Donas #Ga52</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -12533,7 +12533,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Éclairs #dl65</t>
+          <t>Donas #Ga52</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -12554,7 +12554,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Cupcakes #Qm11</t>
+          <t>Brownies #xh72</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -12575,7 +12575,7 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Cupcakes #Qm11</t>
+          <t>Brownies #xh72</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -12596,7 +12596,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Cupcakes #Qm11</t>
+          <t>Brownies #xh72</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -12617,7 +12617,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Cupcakes #Qm11</t>
+          <t>Brownies #xh72</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -12638,7 +12638,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Brownies #fT87</t>
+          <t>Cupcakes #qq88</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -12659,7 +12659,7 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Brownies #fT87</t>
+          <t>Cupcakes #qq88</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -12680,7 +12680,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Brownies #fT87</t>
+          <t>Cupcakes #qq88</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -12701,7 +12701,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Brownies #fT87</t>
+          <t>Cupcakes #qq88</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -12722,7 +12722,7 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Cheesecake #vq56</t>
+          <t>Brownies #Bc74</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -12743,7 +12743,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Cheesecake #vq56</t>
+          <t>Brownies #Bc74</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -12764,7 +12764,7 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Cheesecake #vq56</t>
+          <t>Brownies #Bc74</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -12785,7 +12785,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Cheesecake #vq56</t>
+          <t>Brownies #Bc74</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -12806,7 +12806,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Cheesecake #fJ53</t>
+          <t>Donas #LJ44</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -12827,7 +12827,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Cheesecake #fJ53</t>
+          <t>Donas #LJ44</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -12848,7 +12848,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Cheesecake #fJ53</t>
+          <t>Donas #LJ44</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -12869,7 +12869,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Cheesecake #fJ53</t>
+          <t>Donas #LJ44</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -12890,7 +12890,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Cupcakes #Lv34</t>
+          <t>Brownies #iy55</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -12911,7 +12911,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Cupcakes #Lv34</t>
+          <t>Brownies #iy55</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -12932,7 +12932,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Cupcakes #Lv34</t>
+          <t>Brownies #iy55</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -12953,7 +12953,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Cupcakes #Lv34</t>
+          <t>Brownies #iy55</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -12974,7 +12974,7 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Éclairs #dP72</t>
+          <t>Donas #Vq13</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
@@ -12995,7 +12995,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Éclairs #dP72</t>
+          <t>Donas #Vq13</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -13016,7 +13016,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Éclairs #dP72</t>
+          <t>Donas #Vq13</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -13037,7 +13037,7 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Éclairs #dP72</t>
+          <t>Donas #Vq13</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -13058,7 +13058,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Macarons #je03</t>
+          <t>Pastel de chocolate #FS79</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -13079,7 +13079,7 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Macarons #je03</t>
+          <t>Pastel de chocolate #FS79</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -13100,7 +13100,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Macarons #je03</t>
+          <t>Pastel de chocolate #FS79</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -13121,7 +13121,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Macarons #je03</t>
+          <t>Pastel de chocolate #FS79</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -13142,7 +13142,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Macarons #Uv96</t>
+          <t>Éclairs #MN13</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -13163,7 +13163,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Macarons #Uv96</t>
+          <t>Éclairs #MN13</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -13184,7 +13184,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Macarons #Uv96</t>
+          <t>Éclairs #MN13</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -13205,7 +13205,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Macarons #Uv96</t>
+          <t>Éclairs #MN13</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -13226,7 +13226,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #mB18</t>
+          <t>Cupcakes #AM88</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -13247,7 +13247,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #mB18</t>
+          <t>Cupcakes #AM88</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -13268,7 +13268,7 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #mB18</t>
+          <t>Cupcakes #AM88</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -13289,7 +13289,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #mB18</t>
+          <t>Cupcakes #AM88</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -13310,7 +13310,7 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Tarta de manzana #za59</t>
+          <t>Tarta de manzana #rD15</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -13331,7 +13331,7 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Tarta de manzana #za59</t>
+          <t>Tarta de manzana #rD15</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -13352,7 +13352,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Tarta de manzana #za59</t>
+          <t>Tarta de manzana #rD15</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -13373,7 +13373,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Tarta de manzana #za59</t>
+          <t>Tarta de manzana #rD15</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -13394,7 +13394,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Cheesecake #ge72</t>
+          <t>Éclairs #Ih52</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -13415,7 +13415,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Cheesecake #ge72</t>
+          <t>Éclairs #Ih52</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -13436,7 +13436,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Cheesecake #ge72</t>
+          <t>Éclairs #Ih52</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -13457,7 +13457,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Cheesecake #ge72</t>
+          <t>Éclairs #Ih52</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -13478,7 +13478,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Macarons #cC98</t>
+          <t>Macarons #BL19</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -13499,7 +13499,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Macarons #cC98</t>
+          <t>Macarons #BL19</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -13520,7 +13520,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Macarons #cC98</t>
+          <t>Macarons #BL19</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -13541,7 +13541,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Macarons #cC98</t>
+          <t>Macarons #BL19</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -13562,7 +13562,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Galletas #GJ48</t>
+          <t>Tarta de manzana #RG35</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -13583,7 +13583,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Galletas #GJ48</t>
+          <t>Tarta de manzana #RG35</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -13604,7 +13604,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Galletas #GJ48</t>
+          <t>Tarta de manzana #RG35</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -13625,7 +13625,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Galletas #GJ48</t>
+          <t>Tarta de manzana #RG35</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -13646,7 +13646,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Donas #yw12</t>
+          <t>Tarta de manzana #cs46</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -13667,7 +13667,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Donas #yw12</t>
+          <t>Tarta de manzana #cs46</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -13688,7 +13688,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Donas #yw12</t>
+          <t>Tarta de manzana #cs46</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -13709,7 +13709,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Donas #yw12</t>
+          <t>Tarta de manzana #cs46</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -13730,7 +13730,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Éclairs #nP80</t>
+          <t>Cheesecake #ho66</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -13751,7 +13751,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Éclairs #nP80</t>
+          <t>Cheesecake #ho66</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -13772,7 +13772,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Éclairs #nP80</t>
+          <t>Cheesecake #ho66</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -13793,7 +13793,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Éclairs #nP80</t>
+          <t>Cheesecake #ho66</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -13814,7 +13814,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Cheesecake #NR35</t>
+          <t>Cupcakes #OZ99</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -13835,7 +13835,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Cheesecake #NR35</t>
+          <t>Cupcakes #OZ99</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -13856,7 +13856,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Cheesecake #NR35</t>
+          <t>Cupcakes #OZ99</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -13877,7 +13877,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Cheesecake #NR35</t>
+          <t>Cupcakes #OZ99</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -13898,7 +13898,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Cupcakes #kb55</t>
+          <t>Cupcakes #vv07</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -13919,7 +13919,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Cupcakes #kb55</t>
+          <t>Cupcakes #vv07</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -13940,7 +13940,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Cupcakes #kb55</t>
+          <t>Cupcakes #vv07</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -13961,7 +13961,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Cupcakes #kb55</t>
+          <t>Cupcakes #vv07</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -13982,7 +13982,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Panetone #LM46</t>
+          <t>Panetone #gS17</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -14003,7 +14003,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Panetone #LM46</t>
+          <t>Panetone #gS17</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -14024,7 +14024,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Panetone #LM46</t>
+          <t>Panetone #gS17</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -14045,7 +14045,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Panetone #LM46</t>
+          <t>Panetone #gS17</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -14066,7 +14066,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Brownies #qw71</t>
+          <t>Galletas #Jh57</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -14087,7 +14087,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Brownies #qw71</t>
+          <t>Galletas #Jh57</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -14108,7 +14108,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>Brownies #qw71</t>
+          <t>Galletas #Jh57</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -14129,7 +14129,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Brownies #qw71</t>
+          <t>Galletas #Jh57</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -14150,7 +14150,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Macarons #up08</t>
+          <t>Pastel de chocolate #Qi61</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -14171,7 +14171,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Macarons #up08</t>
+          <t>Pastel de chocolate #Qi61</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -14192,7 +14192,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Macarons #up08</t>
+          <t>Pastel de chocolate #Qi61</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -14213,7 +14213,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Macarons #up08</t>
+          <t>Pastel de chocolate #Qi61</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -14234,7 +14234,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Macarons #kD78</t>
+          <t>Cheesecake #MG68</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -14255,7 +14255,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Macarons #kD78</t>
+          <t>Cheesecake #MG68</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -14276,7 +14276,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Macarons #kD78</t>
+          <t>Cheesecake #MG68</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -14297,7 +14297,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Macarons #kD78</t>
+          <t>Cheesecake #MG68</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -14318,7 +14318,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Panetone #MM27</t>
+          <t>Cheesecake #FB97</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -14339,7 +14339,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Panetone #MM27</t>
+          <t>Cheesecake #FB97</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -14360,7 +14360,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Panetone #MM27</t>
+          <t>Cheesecake #FB97</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -14381,7 +14381,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Panetone #MM27</t>
+          <t>Cheesecake #FB97</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -14402,7 +14402,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Vd05</t>
+          <t>Macarons #yp03</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -14423,7 +14423,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Vd05</t>
+          <t>Macarons #yp03</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -14444,7 +14444,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Vd05</t>
+          <t>Macarons #yp03</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -14465,7 +14465,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Vd05</t>
+          <t>Macarons #yp03</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -14486,7 +14486,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Donas #ez76</t>
+          <t>Panetone #mF39</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -14507,7 +14507,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Donas #ez76</t>
+          <t>Panetone #mF39</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -14528,7 +14528,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Donas #ez76</t>
+          <t>Panetone #mF39</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -14549,7 +14549,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>Donas #ez76</t>
+          <t>Panetone #mF39</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -14570,7 +14570,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>Donas #JX89</t>
+          <t>Cheesecake #Ln34</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -14591,7 +14591,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>Donas #JX89</t>
+          <t>Cheesecake #Ln34</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -14612,7 +14612,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Donas #JX89</t>
+          <t>Cheesecake #Ln34</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -14633,7 +14633,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>Donas #JX89</t>
+          <t>Cheesecake #Ln34</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -14654,7 +14654,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Brownies #tm36</t>
+          <t>Tarta de manzana #hZ28</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -14675,7 +14675,7 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Brownies #tm36</t>
+          <t>Tarta de manzana #hZ28</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -14696,7 +14696,7 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Brownies #tm36</t>
+          <t>Tarta de manzana #hZ28</t>
         </is>
       </c>
       <c r="B680" t="inlineStr">
@@ -14717,7 +14717,7 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>Brownies #tm36</t>
+          <t>Tarta de manzana #hZ28</t>
         </is>
       </c>
       <c r="B681" t="inlineStr">
@@ -14738,7 +14738,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Em92</t>
+          <t>Pastel de chocolate #ko05</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
@@ -14759,7 +14759,7 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Em92</t>
+          <t>Pastel de chocolate #ko05</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
@@ -14780,7 +14780,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Em92</t>
+          <t>Pastel de chocolate #ko05</t>
         </is>
       </c>
       <c r="B684" t="inlineStr">
@@ -14801,7 +14801,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Em92</t>
+          <t>Pastel de chocolate #ko05</t>
         </is>
       </c>
       <c r="B685" t="inlineStr">
@@ -14822,7 +14822,7 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #vF13</t>
+          <t>Brownies #DV36</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
@@ -14843,7 +14843,7 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #vF13</t>
+          <t>Brownies #DV36</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
@@ -14864,7 +14864,7 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #vF13</t>
+          <t>Brownies #DV36</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
@@ -14885,7 +14885,7 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #vF13</t>
+          <t>Brownies #DV36</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
@@ -14906,7 +14906,7 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>Galletas #Ra96</t>
+          <t>Donas #Zy34</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
@@ -14927,7 +14927,7 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Galletas #Ra96</t>
+          <t>Donas #Zy34</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
@@ -14948,7 +14948,7 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>Galletas #Ra96</t>
+          <t>Donas #Zy34</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
@@ -14969,7 +14969,7 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Galletas #Ra96</t>
+          <t>Donas #Zy34</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
@@ -14990,7 +14990,7 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>Cheesecake #mz81</t>
+          <t>Galletas #tT45</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
@@ -15011,7 +15011,7 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>Cheesecake #mz81</t>
+          <t>Galletas #tT45</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
@@ -15032,7 +15032,7 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>Cheesecake #mz81</t>
+          <t>Galletas #tT45</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
@@ -15053,7 +15053,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>Cheesecake #mz81</t>
+          <t>Galletas #tT45</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
@@ -15074,7 +15074,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Brownies #oe46</t>
+          <t>Panetone #BH98</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
@@ -15095,7 +15095,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Brownies #oe46</t>
+          <t>Panetone #BH98</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
@@ -15116,7 +15116,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>Brownies #oe46</t>
+          <t>Panetone #BH98</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
@@ -15137,7 +15137,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>Brownies #oe46</t>
+          <t>Panetone #BH98</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
@@ -15158,7 +15158,7 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Cupcakes #fg99</t>
+          <t>Galletas #Vl54</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
@@ -15179,7 +15179,7 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>Cupcakes #fg99</t>
+          <t>Galletas #Vl54</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
@@ -15200,7 +15200,7 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Cupcakes #fg99</t>
+          <t>Galletas #Vl54</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
@@ -15221,7 +15221,7 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Cupcakes #fg99</t>
+          <t>Galletas #Vl54</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
@@ -15242,7 +15242,7 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #TX74</t>
+          <t>Tarta de manzana #QB80</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
@@ -15263,7 +15263,7 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #TX74</t>
+          <t>Tarta de manzana #QB80</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
@@ -15284,7 +15284,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #TX74</t>
+          <t>Tarta de manzana #QB80</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
@@ -15305,7 +15305,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #TX74</t>
+          <t>Tarta de manzana #QB80</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
@@ -15326,7 +15326,7 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #HZ26</t>
+          <t>Galletas #HA33</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
@@ -15347,7 +15347,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #HZ26</t>
+          <t>Galletas #HA33</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
@@ -15368,7 +15368,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #HZ26</t>
+          <t>Galletas #HA33</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
@@ -15389,7 +15389,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #HZ26</t>
+          <t>Galletas #HA33</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
@@ -15410,7 +15410,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>Cheesecake #Uh08</t>
+          <t>Cupcakes #OP40</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
@@ -15431,7 +15431,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>Cheesecake #Uh08</t>
+          <t>Cupcakes #OP40</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
@@ -15452,7 +15452,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Cheesecake #Uh08</t>
+          <t>Cupcakes #OP40</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
@@ -15473,7 +15473,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>Cheesecake #Uh08</t>
+          <t>Cupcakes #OP40</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
@@ -15494,7 +15494,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>Cupcakes #Tb87</t>
+          <t>Macarons #rM58</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
@@ -15515,7 +15515,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>Cupcakes #Tb87</t>
+          <t>Macarons #rM58</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
@@ -15536,7 +15536,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>Cupcakes #Tb87</t>
+          <t>Macarons #rM58</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
@@ -15557,7 +15557,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>Cupcakes #Tb87</t>
+          <t>Macarons #rM58</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
@@ -15578,7 +15578,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Éclairs #ze92</t>
+          <t>Donas #qi29</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
@@ -15599,7 +15599,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>Éclairs #ze92</t>
+          <t>Donas #qi29</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
@@ -15620,7 +15620,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>Éclairs #ze92</t>
+          <t>Donas #qi29</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
@@ -15641,7 +15641,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>Éclairs #ze92</t>
+          <t>Donas #qi29</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
@@ -15662,7 +15662,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Cupcakes #qa90</t>
+          <t>Macarons #xz32</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
@@ -15683,7 +15683,7 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>Cupcakes #qa90</t>
+          <t>Macarons #xz32</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
@@ -15704,7 +15704,7 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>Cupcakes #qa90</t>
+          <t>Macarons #xz32</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
@@ -15725,7 +15725,7 @@
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>Cupcakes #qa90</t>
+          <t>Macarons #xz32</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
@@ -15746,7 +15746,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>Macarons #rn19</t>
+          <t>Cupcakes #El62</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
@@ -15767,7 +15767,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>Macarons #rn19</t>
+          <t>Cupcakes #El62</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
@@ -15788,7 +15788,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>Macarons #rn19</t>
+          <t>Cupcakes #El62</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
@@ -15809,7 +15809,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>Macarons #rn19</t>
+          <t>Cupcakes #El62</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
@@ -15830,7 +15830,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>Macarons #dp69</t>
+          <t>Macarons #Hv27</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
@@ -15851,7 +15851,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>Macarons #dp69</t>
+          <t>Macarons #Hv27</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
@@ -15872,7 +15872,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>Macarons #dp69</t>
+          <t>Macarons #Hv27</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
@@ -15893,7 +15893,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Macarons #dp69</t>
+          <t>Macarons #Hv27</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
@@ -15914,7 +15914,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>Éclairs #YD15</t>
+          <t>Brownies #Wg34</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
@@ -15935,7 +15935,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>Éclairs #YD15</t>
+          <t>Brownies #Wg34</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
@@ -15956,7 +15956,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>Éclairs #YD15</t>
+          <t>Brownies #Wg34</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
@@ -15977,7 +15977,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>Éclairs #YD15</t>
+          <t>Brownies #Wg34</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
@@ -15998,7 +15998,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>Cupcakes #Fw79</t>
+          <t>Pastel de chocolate #YS37</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
@@ -16019,7 +16019,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>Cupcakes #Fw79</t>
+          <t>Pastel de chocolate #YS37</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
@@ -16040,7 +16040,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>Cupcakes #Fw79</t>
+          <t>Pastel de chocolate #YS37</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
@@ -16061,7 +16061,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>Cupcakes #Fw79</t>
+          <t>Pastel de chocolate #YS37</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
@@ -16082,7 +16082,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #hh18</t>
+          <t>Pastel de chocolate #OA09</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
@@ -16103,7 +16103,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #hh18</t>
+          <t>Pastel de chocolate #OA09</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
@@ -16124,7 +16124,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #hh18</t>
+          <t>Pastel de chocolate #OA09</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
@@ -16145,7 +16145,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #hh18</t>
+          <t>Pastel de chocolate #OA09</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
@@ -16166,7 +16166,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Fq79</t>
+          <t>Galletas #DG19</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
@@ -16187,7 +16187,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Fq79</t>
+          <t>Galletas #DG19</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
@@ -16208,7 +16208,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Fq79</t>
+          <t>Galletas #DG19</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
@@ -16229,7 +16229,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Fq79</t>
+          <t>Galletas #DG19</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
@@ -16250,7 +16250,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>Donas #Od88</t>
+          <t>Brownies #uw04</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
@@ -16271,7 +16271,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>Donas #Od88</t>
+          <t>Brownies #uw04</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -16292,7 +16292,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>Donas #Od88</t>
+          <t>Brownies #uw04</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
@@ -16313,7 +16313,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>Donas #Od88</t>
+          <t>Brownies #uw04</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
@@ -16334,7 +16334,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Uh19</t>
+          <t>Éclairs #QJ83</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
@@ -16355,7 +16355,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Uh19</t>
+          <t>Éclairs #QJ83</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
@@ -16376,7 +16376,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Uh19</t>
+          <t>Éclairs #QJ83</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
@@ -16397,7 +16397,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Uh19</t>
+          <t>Éclairs #QJ83</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
@@ -16418,7 +16418,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Lb25</t>
+          <t>Panetone #JA50</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
@@ -16439,7 +16439,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Lb25</t>
+          <t>Panetone #JA50</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
@@ -16460,7 +16460,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Lb25</t>
+          <t>Panetone #JA50</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
@@ -16481,7 +16481,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>Tarta de manzana #Lb25</t>
+          <t>Panetone #JA50</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
@@ -16502,7 +16502,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>Panetone #Dc83</t>
+          <t>Panetone #yl68</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
@@ -16523,7 +16523,7 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>Panetone #Dc83</t>
+          <t>Panetone #yl68</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
@@ -16544,7 +16544,7 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>Panetone #Dc83</t>
+          <t>Panetone #yl68</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
@@ -16565,7 +16565,7 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>Panetone #Dc83</t>
+          <t>Panetone #yl68</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
@@ -16586,7 +16586,7 @@
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #yW46</t>
+          <t>Cupcakes #MQ95</t>
         </is>
       </c>
       <c r="B770" t="inlineStr">
@@ -16607,7 +16607,7 @@
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #yW46</t>
+          <t>Cupcakes #MQ95</t>
         </is>
       </c>
       <c r="B771" t="inlineStr">
@@ -16628,7 +16628,7 @@
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #yW46</t>
+          <t>Cupcakes #MQ95</t>
         </is>
       </c>
       <c r="B772" t="inlineStr">
@@ -16649,7 +16649,7 @@
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #yW46</t>
+          <t>Cupcakes #MQ95</t>
         </is>
       </c>
       <c r="B773" t="inlineStr">
@@ -16670,7 +16670,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #EO10</t>
+          <t>Cupcakes #gC88</t>
         </is>
       </c>
       <c r="B774" t="inlineStr">
@@ -16691,7 +16691,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #EO10</t>
+          <t>Cupcakes #gC88</t>
         </is>
       </c>
       <c r="B775" t="inlineStr">
@@ -16712,7 +16712,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #EO10</t>
+          <t>Cupcakes #gC88</t>
         </is>
       </c>
       <c r="B776" t="inlineStr">
@@ -16733,7 +16733,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #EO10</t>
+          <t>Cupcakes #gC88</t>
         </is>
       </c>
       <c r="B777" t="inlineStr">
@@ -16754,7 +16754,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>Cupcakes #uY45</t>
+          <t>Tarta de manzana #zO53</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -16775,7 +16775,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>Cupcakes #uY45</t>
+          <t>Tarta de manzana #zO53</t>
         </is>
       </c>
       <c r="B779" t="inlineStr">
@@ -16796,7 +16796,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>Cupcakes #uY45</t>
+          <t>Tarta de manzana #zO53</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
@@ -16817,7 +16817,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>Cupcakes #uY45</t>
+          <t>Tarta de manzana #zO53</t>
         </is>
       </c>
       <c r="B781" t="inlineStr">
@@ -16838,7 +16838,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Eb35</t>
+          <t>Macarons #Ks16</t>
         </is>
       </c>
       <c r="B782" t="inlineStr">
@@ -16859,7 +16859,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Eb35</t>
+          <t>Macarons #Ks16</t>
         </is>
       </c>
       <c r="B783" t="inlineStr">
@@ -16880,7 +16880,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Eb35</t>
+          <t>Macarons #Ks16</t>
         </is>
       </c>
       <c r="B784" t="inlineStr">
@@ -16901,7 +16901,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>Pastel de chocolate #Eb35</t>
+          <t>Macarons #Ks16</t>
         </is>
       </c>
       <c r="B785" t="inlineStr">
@@ -16922,7 +16922,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>Cupcakes #tJ06</t>
+          <t>Tarta de manzana #ae68</t>
         </is>
       </c>
       <c r="B786" t="inlineStr">
@@ -16943,7 +16943,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>Cupcakes #tJ06</t>
+          <t>Tarta de manzana #ae68</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -16964,7 +16964,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>Cupcakes #tJ06</t>
+          <t>Tarta de manzana #ae68</t>
         </is>
       </c>
       <c r="B788" t="inlineStr">
@@ -16985,7 +16985,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>Cupcakes #tJ06</t>
+          <t>Tarta de manzana #ae68</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
@@ -17006,7 +17006,7 @@
     <row r="790">
       <c r="A790" t="inlineStr">
         <is>
-          <t>Panetone #gU82</t>
+          <t>Pastel de chocolate #FP59</t>
         </is>
       </c>
       <c r="B790" t="inlineStr">
@@ -17027,7 +17027,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>Panetone #gU82</t>
+          <t>Pastel de chocolate #FP59</t>
         </is>
       </c>
       <c r="B791" t="inlineStr">
@@ -17048,7 +17048,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>Panetone #gU82</t>
+          <t>Pastel de chocolate #FP59</t>
         </is>
       </c>
       <c r="B792" t="inlineStr">
@@ -17069,7 +17069,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>Panetone #gU82</t>
+          <t>Pastel de chocolate #FP59</t>
         </is>
       </c>
       <c r="B793" t="inlineStr">
@@ -17090,7 +17090,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>Donas #eJ49</t>
+          <t>Galletas #pJ01</t>
         </is>
       </c>
       <c r="B794" t="inlineStr">
@@ -17111,7 +17111,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>Donas #eJ49</t>
+          <t>Galletas #pJ01</t>
         </is>
       </c>
       <c r="B795" t="inlineStr">
@@ -17132,7 +17132,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>Donas #eJ49</t>
+          <t>Galletas #pJ01</t>
         </is>
       </c>
       <c r="B796" t="inlineStr">
@@ -17153,7 +17153,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>Donas #eJ49</t>
+          <t>Galletas #pJ01</t>
         </is>
       </c>
       <c r="B797" t="inlineStr">
@@ -17174,7 +17174,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>Panetone #Pl77</t>
+          <t>Galletas #CH93</t>
         </is>
       </c>
       <c r="B798" t="inlineStr">
@@ -17195,7 +17195,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>Panetone #Pl77</t>
+          <t>Galletas #CH93</t>
         </is>
       </c>
       <c r="B799" t="inlineStr">
@@ -17216,7 +17216,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>Panetone #Pl77</t>
+          <t>Galletas #CH93</t>
         </is>
       </c>
       <c r="B800" t="inlineStr">
@@ -17237,7 +17237,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>Panetone #Pl77</t>
+          <t>Galletas #CH93</t>
         </is>
       </c>
       <c r="B801" t="inlineStr">
